--- a/molecule_synthesis/runs/seh_paper_medium/rgfn/seed_0/batch/modes/modes_0.xlsx
+++ b/molecule_synthesis/runs/seh_paper_medium/rgfn/seed_0/batch/modes/modes_0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
   <si>
     <t>Molecule</t>
   </si>
@@ -46,118 +46,121 @@
     <t>SMILES</t>
   </si>
   <si>
-    <t>8.23</t>
-  </si>
-  <si>
-    <t>8.21</t>
-  </si>
-  <si>
-    <t>8.11</t>
-  </si>
-  <si>
-    <t>8.10</t>
-  </si>
-  <si>
-    <t>8.03</t>
+    <t>8.28</t>
+  </si>
+  <si>
+    <t>8.19</t>
+  </si>
+  <si>
+    <t>8.17</t>
+  </si>
+  <si>
+    <t>8.05</t>
+  </si>
+  <si>
+    <t>8.04</t>
+  </si>
+  <si>
+    <t>8.02</t>
   </si>
   <si>
     <t>8.01</t>
   </si>
   <si>
-    <t>470.23</t>
-  </si>
-  <si>
-    <t>464.23</t>
-  </si>
-  <si>
-    <t>441.24</t>
-  </si>
-  <si>
-    <t>515.24</t>
-  </si>
-  <si>
-    <t>532.28</t>
-  </si>
-  <si>
-    <t>503.24</t>
-  </si>
-  <si>
-    <t>523.28</t>
-  </si>
-  <si>
-    <t>553.26</t>
-  </si>
-  <si>
-    <t>3.431</t>
-  </si>
-  <si>
-    <t>4.921</t>
-  </si>
-  <si>
-    <t>2.831</t>
-  </si>
-  <si>
-    <t>5.354</t>
-  </si>
-  <si>
-    <t>4.274</t>
-  </si>
-  <si>
-    <t>5.263</t>
-  </si>
-  <si>
-    <t>3.258</t>
-  </si>
-  <si>
-    <t>4.844</t>
-  </si>
-  <si>
-    <t>0.2350</t>
-  </si>
-  <si>
-    <t>0.2347</t>
-  </si>
-  <si>
-    <t>0.2459</t>
-  </si>
-  <si>
-    <t>0.2078</t>
-  </si>
-  <si>
-    <t>0.2025</t>
+    <t>533.28</t>
+  </si>
+  <si>
+    <t>443.19</t>
+  </si>
+  <si>
+    <t>508.24</t>
+  </si>
+  <si>
+    <t>481.23</t>
+  </si>
+  <si>
+    <t>544.24</t>
+  </si>
+  <si>
+    <t>504.24</t>
+  </si>
+  <si>
+    <t>381.20</t>
+  </si>
+  <si>
+    <t>520.23</t>
+  </si>
+  <si>
+    <t>3.669</t>
+  </si>
+  <si>
+    <t>4.569</t>
+  </si>
+  <si>
+    <t>3.534</t>
+  </si>
+  <si>
+    <t>5.377</t>
+  </si>
+  <si>
+    <t>4.559</t>
+  </si>
+  <si>
+    <t>4.682</t>
+  </si>
+  <si>
+    <t>5.029</t>
+  </si>
+  <si>
+    <t>6.098</t>
+  </si>
+  <si>
+    <t>0.2071</t>
+  </si>
+  <si>
+    <t>0.2483</t>
+  </si>
+  <si>
+    <t>0.2150</t>
+  </si>
+  <si>
+    <t>0.2334</t>
+  </si>
+  <si>
+    <t>0.1963</t>
   </si>
   <si>
     <t>0.2114</t>
   </si>
   <si>
-    <t>0.2059</t>
-  </si>
-  <si>
-    <t>0.2003</t>
-  </si>
-  <si>
-    <t>O=C(Nc1cc(-c2cccc(NCc3ccc(-c4nnn(CC5CC5)n4)nc3)c2)n[nH]1)NC1CC1</t>
-  </si>
-  <si>
-    <t>O=C(NC1CC1)c1ccc(CNc2ccc(-c3cccc(-c4nnn(CC5CC5)n4)c3)cc2)cc1</t>
-  </si>
-  <si>
-    <t>c1cc(-c2nnn(CC3CC3)n2)ccc1Cn1cc(-c2ccc(NCC3CCN3)cc2)nn1</t>
-  </si>
-  <si>
-    <t>O=C(NCc1ccccc1)c1cccc(-c2ccc(NCc3ccc(-c4nnn(CC5CC5)n4)nc3)cc2)c1</t>
-  </si>
-  <si>
-    <t>c1ccc2c(c1)CN[C@H](CNc1ccccc1-c1cc(NCc3ccc(-c4nnn(CC5CC5)n4)nc3)[nH]n1)C2</t>
-  </si>
-  <si>
-    <t>O=C(Nc1ccc(-c2cc(NCC3CCN3)[nH]n2)cc1)c1ccc(CNc2ccnc3ccccc23)cc1</t>
-  </si>
-  <si>
-    <t>O=C(Nc1cc(-c2cccc(-c3nnn(CC4CC4)n3)c2)n[nH]1)[C@H]1CCCN1C[C@@H]1Cc2ccccc2CN1</t>
-  </si>
-  <si>
-    <t>O=C(Nc1ccc(-c2ccc(-c3nnn(CC4CC4)n3)s2)cc1)[C@H]1CCCN(C[C@@H]2Cc3ccccc3CN2)C1</t>
+    <t>0.2765</t>
+  </si>
+  <si>
+    <t>0.2053</t>
+  </si>
+  <si>
+    <t>c1ccc2c(c1)CN[C@H](CNc1cc(-c3ccc(NCc4ccc(-c5nnn(CC6CC6)n5)nc4)nc3)n[nH]1)C2</t>
+  </si>
+  <si>
+    <t>O=C(Nc1cc(-c2cccc(NCc3ccc(-c4cnc(F)nc4)cc3)c2)n[nH]1)NC1CC1</t>
+  </si>
+  <si>
+    <t>O=C(Nc1cc(-c2cccc(NCc3c[nH]c4ccc(-c5nnn(CC6CC6)n5)cc34)c2)n[nH]1)C1CCN1</t>
+  </si>
+  <si>
+    <t>c1cc(NCC2CCN2)cc(-c2csc(-c3ccc(NC[C@@H]4Cc5ccccc5CN4)cc3)n2)c1</t>
+  </si>
+  <si>
+    <t>O=C(NCc1c[nH]c2ccccc12)c1ccc(CNc2cc(-c3ccc(-c4nnn(CC5CC5)n4)nc3)n[nH]2)cc1</t>
+  </si>
+  <si>
+    <t>O=C(Nc1cc(-c2cccc(-c3nnn(CC4CC4)n3)c2)n[nH]1)c1ccc(CNCc2ccccc2)cc1</t>
+  </si>
+  <si>
+    <t>c1cncc(-c2cccc(CNc3ccc(-c4cn(CC5CC5)nn4)cc3)c2)c1</t>
+  </si>
+  <si>
+    <t>O=C(Nc1ccc(NCc2c[nH]c3ccccc23)cc1)Nc1cccc(-c2cc(NC(=O)NC3CC3)[nH]n2)c1</t>
   </si>
 </sst>
 </file>
@@ -868,28 +871,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>4</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="120" customHeight="1">
@@ -897,28 +900,28 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="120" customHeight="1">
@@ -926,28 +929,28 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4">
         <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="120" customHeight="1">
@@ -955,28 +958,28 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="120" customHeight="1">
@@ -984,28 +987,28 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6">
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="120" customHeight="1">
@@ -1013,86 +1016,86 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="120" customHeight="1">
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8" t="s">
         <v>39</v>
       </c>
-      <c r="G8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8" t="s">
-        <v>38</v>
-      </c>
       <c r="J8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="120" customHeight="1">
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H9">
         <v>8</v>
       </c>
       <c r="I9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
